--- a/learning/02-sql-learning/sql-analyst-lab/01-brew-and-co/work/00-running-log.xlsx
+++ b/learning/02-sql-learning/sql-analyst-lab/01-brew-and-co/work/00-running-log.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Big Question</t>
   </si>
@@ -23,6 +23,24 @@
   </si>
   <si>
     <t>Why</t>
+  </si>
+  <si>
+    <t>How is sales performance, and where should we focus next month?</t>
+  </si>
+  <si>
+    <t>What is the chain-wide Revenue trend over time? | Revenue · Month</t>
+  </si>
+  <si>
+    <t>The trend shows a temporary rise in May 2025, followed by a decline over the next seven months, before rising again in 2026.</t>
+  </si>
+  <si>
+    <t>How is Revenue split across menu categories? | Revenue · Category</t>
+  </si>
+  <si>
+    <t>How is Revenue split across the 3 stores? | Revenue · Store</t>
+  </si>
+  <si>
+    <t>The revenue trend tends to be stable (experiencing fluctuations that are not particularly significant).</t>
   </si>
 </sst>
 </file>
@@ -46,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -54,15 +72,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,12 +451,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="23.428571428571427" customWidth="1"/>
-    <col min="2" max="2" width="21.857142857142858" customWidth="1"/>
-    <col min="3" max="26" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="18.714285714285715" customWidth="1"/>
+    <col min="2" max="2" width="23.142857142857142" customWidth="1"/>
+    <col min="3" max="3" width="15.857142857142858" customWidth="1"/>
+    <col min="4" max="4" width="14.428571428571429" customWidth="1"/>
+    <col min="5" max="26" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -422,6 +473,48 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/learning/02-sql-learning/sql-analyst-lab/01-brew-and-co/work/00-running-log.xlsx
+++ b/learning/02-sql-learning/sql-analyst-lab/01-brew-and-co/work/00-running-log.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>Big Question</t>
   </si>
@@ -31,27 +31,25 @@
     <t>What is the chain-wide Revenue trend over time? | Revenue · Month</t>
   </si>
   <si>
-    <t>The trend shows a temporary rise in May 2025, followed by a decline over the next seven months, before rising again in 2026.</t>
-  </si>
-  <si>
     <t>How is Revenue split across menu categories? | Revenue · Category</t>
   </si>
   <si>
     <t>How is Revenue split across the 3 stores? | Revenue · Store</t>
-  </si>
-  <si>
-    <t>The revenue trend tends to be stable (experiencing fluctuations that are not particularly significant).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -73,31 +71,55 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -106,12 +128,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,11 +476,11 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18.714285714285715" customWidth="1"/>
-    <col min="2" max="2" width="23.142857142857142" customWidth="1"/>
+    <col min="1" max="1" width="43.42857142857143" customWidth="1"/>
+    <col min="2" max="2" width="38.42857142857143" customWidth="1"/>
     <col min="3" max="3" width="15.857142857142858" customWidth="1"/>
     <col min="4" max="4" width="14.428571428571429" customWidth="1"/>
-    <col min="5" max="26" width="13.571428571428571" customWidth="1"/>
+    <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -482,9 +504,7 @@
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -492,7 +512,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -502,21 +522,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
